--- a/注塑项目/金榕/上海金榕- TPE脚垫卡扣项目/内部_产品报价_TPE脚垫卡扣_20260707(1).xlsx
+++ b/注塑项目/金榕/上海金榕- TPE脚垫卡扣项目/内部_产品报价_TPE脚垫卡扣_20260707(1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chensiyuan5/Desktop/Github/shenyuan_work/注塑项目/金榕/上海金榕- TPE脚垫卡扣项目/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83B6C25-D7C0-0B45-B975-D90CAAE98476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD8452D4-3F44-1847-968C-40C89C0CD8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="600" windowWidth="40960" windowHeight="18520" tabRatio="566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17240" tabRatio="566" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="最终报价" sheetId="2" r:id="rId1"/>
@@ -277,22 +277,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="16">
-    <numFmt numFmtId="166" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
-    <numFmt numFmtId="169" formatCode="0.00_ "/>
-    <numFmt numFmtId="170" formatCode="\¥#,##0.00_);[Red]\(\¥#,##0.00\)"/>
-    <numFmt numFmtId="171" formatCode="\¥#,##0_);[Red]\(\¥#,##0\)"/>
-    <numFmt numFmtId="172" formatCode="0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="174" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
-    <numFmt numFmtId="175" formatCode="#,##0_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.000_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
-    <numFmt numFmtId="179" formatCode="0.0%"/>
-    <numFmt numFmtId="180" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="181" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??.0000_ ;_ @_ "/>
-    <numFmt numFmtId="182" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
+    <numFmt numFmtId="166" formatCode="0.00_ "/>
+    <numFmt numFmtId="167" formatCode="\¥#,##0.00_);[Red]\(\¥#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="\¥#,##0_);[Red]\(\¥#,##0\)"/>
+    <numFmt numFmtId="169" formatCode="0.0000_ "/>
+    <numFmt numFmtId="170" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="171" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??.00_ ;_ @_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0_ "/>
+    <numFmt numFmtId="173" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="174" formatCode="#,##0.000_ "/>
+    <numFmt numFmtId="175" formatCode="#,##0.0000_);[Red]\(#,##0.0000\)"/>
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.0000_ ;_ * \-#,##0.0000_ ;_ * &quot;-&quot;??.0000_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -328,7 +328,7 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -340,13 +340,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -356,7 +356,8 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="14"/>
@@ -532,9 +533,9 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -614,79 +615,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="5" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="3" fillId="5" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="3" fillId="5" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="1" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="5" fillId="0" borderId="1" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="1" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -708,47 +709,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="174" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -761,111 +758,115 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="4" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="8" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="15" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="20" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="3" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="2" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="4" borderId="1" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="20" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -883,14 +884,7 @@
     <cellStyle name="常规_Sheet1" xfId="8" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="样式 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1091,25 +1085,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="18"/>
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="totalRow" dxfId="16"/>
-      <tableStyleElement type="firstColumn" dxfId="15"/>
-      <tableStyleElement type="lastColumn" dxfId="14"/>
-      <tableStyleElement type="firstRowStripe" dxfId="13"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="12"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="totalRow" dxfId="10"/>
-      <tableStyleElement type="firstRowStripe" dxfId="9"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="7"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="6"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="5"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="4"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="3"/>
-      <tableStyleElement type="pageFieldValues" dxfId="2"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1433,328 +1427,328 @@
   <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:64" s="74" customFormat="1" ht="19" customHeight="1">
-      <c r="A1" s="65"/>
-      <c r="B1" s="65" t="s">
+    <row r="1" spans="1:64" s="71" customFormat="1" ht="19" customHeight="1">
+      <c r="A1" s="63"/>
+      <c r="B1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="66"/>
-      <c r="D1" s="67" t="s">
+      <c r="C1" s="64"/>
+      <c r="D1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="68" t="s">
+      <c r="E1" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="69"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
-      <c r="Z1" s="70"/>
-      <c r="AA1" s="66"/>
-      <c r="AB1" s="70"/>
-      <c r="AC1" s="66"/>
-      <c r="AD1" s="70"/>
-      <c r="AE1" s="70"/>
-      <c r="AF1" s="70"/>
-      <c r="AG1" s="70"/>
-      <c r="AH1" s="70"/>
-      <c r="AI1" s="70"/>
-      <c r="AJ1" s="70"/>
-      <c r="AK1" s="70"/>
-      <c r="AL1" s="70"/>
-      <c r="AM1" s="70"/>
-      <c r="AN1" s="70"/>
-      <c r="AO1" s="70"/>
-      <c r="AP1" s="70"/>
-      <c r="AQ1" s="71"/>
-      <c r="AR1" s="71"/>
-      <c r="AS1" s="71"/>
-      <c r="AT1" s="71"/>
-      <c r="AU1" s="71"/>
-      <c r="AV1" s="71"/>
-      <c r="AW1" s="71"/>
-      <c r="AX1" s="71"/>
-      <c r="AY1" s="71"/>
-      <c r="AZ1" s="70"/>
-      <c r="BA1" s="70"/>
-      <c r="BB1" s="70"/>
-      <c r="BC1" s="72"/>
-      <c r="BD1" s="73"/>
-      <c r="BE1" s="73"/>
-      <c r="BF1" s="73"/>
-      <c r="BG1" s="73"/>
-      <c r="BH1" s="73"/>
-      <c r="BI1" s="73"/>
-      <c r="BJ1" s="73"/>
-      <c r="BK1" s="71"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="98"/>
+      <c r="H1" s="98"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="98"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="64"/>
+      <c r="AD1" s="67"/>
+      <c r="AE1" s="67"/>
+      <c r="AF1" s="67"/>
+      <c r="AG1" s="67"/>
+      <c r="AH1" s="67"/>
+      <c r="AI1" s="67"/>
+      <c r="AJ1" s="67"/>
+      <c r="AK1" s="67"/>
+      <c r="AL1" s="67"/>
+      <c r="AM1" s="67"/>
+      <c r="AN1" s="67"/>
+      <c r="AO1" s="67"/>
+      <c r="AP1" s="67"/>
+      <c r="AQ1" s="68"/>
+      <c r="AR1" s="68"/>
+      <c r="AS1" s="68"/>
+      <c r="AT1" s="68"/>
+      <c r="AU1" s="68"/>
+      <c r="AV1" s="68"/>
+      <c r="AW1" s="68"/>
+      <c r="AX1" s="68"/>
+      <c r="AY1" s="68"/>
+      <c r="AZ1" s="67"/>
+      <c r="BA1" s="67"/>
+      <c r="BB1" s="67"/>
+      <c r="BC1" s="69"/>
+      <c r="BD1" s="70"/>
+      <c r="BE1" s="70"/>
+      <c r="BF1" s="70"/>
+      <c r="BG1" s="70"/>
+      <c r="BH1" s="70"/>
+      <c r="BI1" s="70"/>
+      <c r="BJ1" s="70"/>
+      <c r="BK1" s="68"/>
     </row>
-    <row r="2" spans="1:64" s="75" customFormat="1" ht="44" customHeight="1">
-      <c r="B2" s="76"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="82"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="80"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="83"/>
-      <c r="AN2" s="84" t="s">
+    <row r="2" spans="1:64" s="72" customFormat="1" ht="44" customHeight="1">
+      <c r="B2" s="73"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="78"/>
+      <c r="Y2" s="78"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="77"/>
+      <c r="AB2" s="80"/>
+      <c r="AC2" s="77"/>
+      <c r="AD2" s="80"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="80"/>
+      <c r="AG2" s="80"/>
+      <c r="AH2" s="80"/>
+      <c r="AI2" s="80"/>
+      <c r="AJ2" s="80"/>
+      <c r="AK2" s="80"/>
+      <c r="AL2" s="80"/>
+      <c r="AM2" s="80"/>
+      <c r="AN2" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="AO2" s="63"/>
-      <c r="AP2" s="83"/>
-      <c r="AQ2" s="83"/>
-      <c r="AR2" s="71"/>
-      <c r="AS2" s="85" t="s">
+      <c r="AO2" s="96"/>
+      <c r="AP2" s="80"/>
+      <c r="AQ2" s="80"/>
+      <c r="AR2" s="68"/>
+      <c r="AS2" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="AT2" s="63"/>
-      <c r="AU2" s="85" t="s">
+      <c r="AT2" s="96"/>
+      <c r="AU2" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="AV2" s="63"/>
-      <c r="AW2" s="85" t="s">
+      <c r="AV2" s="96"/>
+      <c r="AW2" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="AX2" s="63"/>
-      <c r="AY2" s="85" t="s">
+      <c r="AX2" s="96"/>
+      <c r="AY2" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="AZ2" s="63"/>
-      <c r="BA2" s="85" t="s">
+      <c r="AZ2" s="96"/>
+      <c r="BA2" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="BB2" s="63"/>
-      <c r="BC2" s="86"/>
-      <c r="BD2" s="87"/>
-      <c r="BE2" s="87"/>
-      <c r="BF2" s="87"/>
-      <c r="BG2" s="87"/>
-      <c r="BH2" s="87"/>
-      <c r="BI2" s="87"/>
-      <c r="BJ2" s="87"/>
-      <c r="BK2" s="83"/>
+      <c r="BB2" s="96"/>
+      <c r="BC2" s="81"/>
+      <c r="BD2" s="82"/>
+      <c r="BE2" s="82"/>
+      <c r="BF2" s="82"/>
+      <c r="BG2" s="82"/>
+      <c r="BH2" s="82"/>
+      <c r="BI2" s="82"/>
+      <c r="BJ2" s="82"/>
+      <c r="BK2" s="80"/>
     </row>
-    <row r="3" spans="1:64" s="99" customFormat="1" ht="68" customHeight="1">
-      <c r="A3" s="88" t="s">
+    <row r="3" spans="1:64" s="94" customFormat="1" ht="68" customHeight="1">
+      <c r="A3" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="88" t="s">
+      <c r="B3" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="88" t="s">
+      <c r="C3" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="88" t="s">
+      <c r="D3" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="88" t="s">
+      <c r="E3" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="88" t="s">
+      <c r="F3" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="88" t="s">
+      <c r="G3" s="83" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="89" t="s">
+      <c r="H3" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="89" t="s">
+      <c r="I3" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="89" t="s">
+      <c r="J3" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="89" t="s">
+      <c r="K3" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="89" t="s">
+      <c r="L3" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="89" t="s">
+      <c r="M3" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="90" t="s">
+      <c r="N3" s="85" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="89" t="s">
+      <c r="O3" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="89" t="s">
+      <c r="P3" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="89" t="s">
+      <c r="Q3" s="84" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="89" t="s">
+      <c r="R3" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="S3" s="89" t="s">
+      <c r="S3" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="89" t="s">
+      <c r="T3" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="U3" s="89" t="s">
+      <c r="U3" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="V3" s="89" t="s">
+      <c r="V3" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="89" t="s">
+      <c r="W3" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="X3" s="89" t="s">
+      <c r="X3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="Y3" s="89" t="s">
+      <c r="Y3" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="Z3" s="91" t="s">
+      <c r="Z3" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="AA3" s="89" t="s">
+      <c r="AA3" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="AB3" s="91" t="s">
+      <c r="AB3" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="AC3" s="89" t="s">
+      <c r="AC3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="AD3" s="91" t="s">
+      <c r="AD3" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="AE3" s="91" t="s">
+      <c r="AE3" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="AF3" s="91"/>
-      <c r="AG3" s="91" t="s">
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="AH3" s="91"/>
-      <c r="AI3" s="91" t="s">
+      <c r="AH3" s="86"/>
+      <c r="AI3" s="86" t="s">
         <v>40</v>
       </c>
-      <c r="AJ3" s="91" t="s">
+      <c r="AJ3" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="AK3" s="91" t="s">
+      <c r="AK3" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="AL3" s="91" t="s">
+      <c r="AL3" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="AM3" s="92" t="s">
+      <c r="AM3" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="AN3" s="92" t="s">
+      <c r="AN3" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="AO3" s="92" t="s">
+      <c r="AO3" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="AP3" s="93" t="s">
+      <c r="AP3" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="AQ3" s="91" t="s">
+      <c r="AQ3" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="AR3" s="94"/>
-      <c r="AS3" s="95"/>
-      <c r="AT3" s="91" t="s">
+      <c r="AR3" s="89"/>
+      <c r="AS3" s="90"/>
+      <c r="AT3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="AU3" s="95"/>
-      <c r="AV3" s="91" t="s">
+      <c r="AU3" s="90"/>
+      <c r="AV3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="AW3" s="95"/>
-      <c r="AX3" s="91" t="s">
+      <c r="AW3" s="90"/>
+      <c r="AX3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="AY3" s="95"/>
-      <c r="AZ3" s="91" t="s">
+      <c r="AY3" s="90"/>
+      <c r="AZ3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="BA3" s="95"/>
-      <c r="BB3" s="91" t="s">
+      <c r="BA3" s="90"/>
+      <c r="BB3" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="BC3" s="96" t="s">
+      <c r="BC3" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="BD3" s="96" t="s">
+      <c r="BD3" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="BE3" s="96" t="s">
+      <c r="BE3" s="91" t="s">
         <v>52</v>
       </c>
-      <c r="BF3" s="96" t="s">
+      <c r="BF3" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="BG3" s="96" t="s">
+      <c r="BG3" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="BH3" s="96" t="s">
+      <c r="BH3" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="BI3" s="96" t="s">
+      <c r="BI3" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="BJ3" s="96" t="s">
+      <c r="BJ3" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="BK3" s="97" t="s">
+      <c r="BK3" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="BL3" s="98" t="s">
+      <c r="BL3" s="93" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1943,7 +1937,7 @@
       <c r="BK4" s="43"/>
       <c r="BL4" s="43"/>
     </row>
-    <row r="5" spans="1:64" ht="75">
+    <row r="5" spans="1:64" ht="45">
       <c r="A5" s="2">
         <v>2</v>
       </c>
